--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N95_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.41147595293407</v>
+        <v>5.754364842351786</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2093262206762</v>
+        <v>5.721515510859883</v>
       </c>
       <c r="E2" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F2" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.7775759191021</v>
+        <v>2.401356086854091</v>
       </c>
       <c r="D3" t="n">
-        <v>14.49465231219511</v>
+        <v>2.355381000731705</v>
       </c>
       <c r="E3" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F3" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.39658960944201</v>
+        <v>4.776945811534326</v>
       </c>
       <c r="D4" t="n">
-        <v>29.4016068559727</v>
+        <v>4.777761114095564</v>
       </c>
       <c r="E4" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F4" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.59362814901988</v>
+        <v>11.30896457421573</v>
       </c>
       <c r="D5" t="n">
-        <v>68.93601244586131</v>
+        <v>11.20210202245246</v>
       </c>
       <c r="E5" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F5" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.40063166734861</v>
+        <v>4.615102645944149</v>
       </c>
       <c r="D6" t="n">
-        <v>28.29425978900033</v>
+        <v>4.597817215712554</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F6" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.54660220818165</v>
+        <v>7.401322858829518</v>
       </c>
       <c r="D7" t="n">
-        <v>44.87425582411552</v>
+        <v>7.292066571418773</v>
       </c>
       <c r="E7" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F7" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.42005443224974</v>
+        <v>5.430758845240582</v>
       </c>
       <c r="D8" t="n">
-        <v>34.02535368997841</v>
+        <v>5.529119974621492</v>
       </c>
       <c r="E8" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F8" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.10959974409193</v>
+        <v>1.642809958414938</v>
       </c>
       <c r="D9" t="n">
-        <v>10.76910494322415</v>
+        <v>1.749979553273925</v>
       </c>
       <c r="E9" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F9" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.20162351626772</v>
+        <v>6.532763821393505</v>
       </c>
       <c r="D10" t="n">
-        <v>39.60999188730658</v>
+        <v>6.43662368168732</v>
       </c>
       <c r="E10" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F10" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.34325502843576</v>
+        <v>4.118278942120812</v>
       </c>
       <c r="D11" t="n">
-        <v>25.43952208304871</v>
+        <v>4.133922338495417</v>
       </c>
       <c r="E11" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F11" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.63201876402085</v>
+        <v>5.952703049153389</v>
       </c>
       <c r="D12" t="n">
-        <v>37.22200682280415</v>
+        <v>6.048576108705674</v>
       </c>
       <c r="E12" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F12" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.659047629133635</v>
+        <v>1.569595239734216</v>
       </c>
       <c r="D13" t="n">
-        <v>10.57836801234788</v>
+        <v>1.71898480200653</v>
       </c>
       <c r="E13" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F13" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>36.38768606702074</v>
+        <v>5.912998985890871</v>
       </c>
       <c r="D14" t="n">
-        <v>35.28729042247576</v>
+        <v>5.734184693652312</v>
       </c>
       <c r="E14" t="n">
-        <v>15.33545072721973</v>
+        <v>2.492010743173206</v>
       </c>
       <c r="F14" t="n">
-        <v>14.98650096756073</v>
+        <v>2.435306407228619</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
